--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h2.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h2.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>1.0235</v>
       </c>
       <c r="F2">
-        <v>0.9179</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.1056</v>
+        <v>-0.0541</v>
       </c>
       <c r="H2">
-        <v>-0.017</v>
+        <v>0.3619</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K2">
+        <v>22</v>
+      </c>
+      <c r="L2">
         <v>28</v>
-      </c>
-      <c r="L2">
-        <v>22</v>
       </c>
       <c r="M2">
         <v>50</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.9666</v>
+        <v>1.0975</v>
       </c>
       <c r="F3">
-        <v>0.7809</v>
+        <v>0.8669</v>
       </c>
       <c r="G3">
-        <v>-0.1857</v>
+        <v>-0.2305</v>
       </c>
       <c r="H3">
-        <v>-0.5841</v>
+        <v>-0.4741</v>
       </c>
       <c r="I3">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>1.3223</v>
+        <v>0.9213</v>
       </c>
       <c r="F4">
-        <v>1.6368</v>
+        <v>1.1107</v>
       </c>
       <c r="G4">
-        <v>0.3145</v>
+        <v>0.1894</v>
       </c>
       <c r="H4">
-        <v>2.9602</v>
+        <v>1.5164</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N4">
         <v>2</v>
